--- a/Test-Cases/Test Cases - Automation Exercise.xlsx
+++ b/Test-Cases/Test Cases - Automation Exercise.xlsx
@@ -4,6 +4,8 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="Login and Logout" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Registration" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Test Data" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,11 +13,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="366">
   <si>
     <t>Test Case ID</t>
   </si>
   <si>
+    <t>SECTION 1: Data set REG-VALID (valid registration data)</t>
+  </si>
+  <si>
     <t>Scenario ID</t>
   </si>
   <si>
@@ -34,9 +39,15 @@
     <t>Test Data</t>
   </si>
   <si>
+    <t>Field</t>
+  </si>
+  <si>
     <t>Steps</t>
   </si>
   <si>
+    <t>Value</t>
+  </si>
+  <si>
     <t>Expected Result</t>
   </si>
   <si>
@@ -46,76 +57,233 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Mrs.</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>First name</t>
+  </si>
+  <si>
+    <t>Lara</t>
+  </si>
+  <si>
+    <t>Last name</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>TC-REG-01</t>
+  </si>
+  <si>
+    <t>123 Test Street</t>
+  </si>
+  <si>
+    <t>TS-REG-01</t>
+  </si>
+  <si>
+    <t>FR-REG-03</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
     <t>TC-LOG-01</t>
   </si>
   <si>
+    <t>[actual default, e.g., India]</t>
+  </si>
+  <si>
+    <t>Registration</t>
+  </si>
+  <si>
     <t>TS-LOG-01</t>
   </si>
   <si>
+    <t>Display "Enter Account Information" page</t>
+  </si>
+  <si>
     <t>FR-LOG-01</t>
   </si>
   <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.nocreate01@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
     <t>Login and Logout</t>
   </si>
   <si>
+    <t>Test State</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.nocreate01@mailinator.com</t>
+  </si>
+  <si>
     <t>Display a login form</t>
   </si>
   <si>
+    <t>1. Under "New User Signup!", enter the name and email. 2. Click Signup.</t>
+  </si>
+  <si>
     <t>1. The user is logged out. 2. The Home page is open in Chrome.</t>
   </si>
   <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>The "Enter Account Information" page is displayed.</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Test City</t>
+  </si>
+  <si>
     <t xml:space="preserve">1. Click Signup / Login in the header. </t>
   </si>
   <si>
+    <t>Not Run</t>
+  </si>
+  <si>
     <t>The system displays a login form with Email Address and Password fields and a Login button.</t>
   </si>
   <si>
     <t>Medium</t>
   </si>
   <si>
-    <t>Not Run</t>
+    <t>TC-REG-02</t>
+  </si>
+  <si>
+    <t>TS-REG-02</t>
+  </si>
+  <si>
+    <t>FR-REG-06</t>
+  </si>
+  <si>
+    <t>Zipcode</t>
   </si>
   <si>
     <t>TC-LOG-02</t>
   </si>
   <si>
+    <t>Email on the "Enter Account Information" page is locked</t>
+  </si>
+  <si>
     <t>TS-LOG-02</t>
   </si>
   <si>
     <t>FR-LOG-04, FR-LOG-07</t>
   </si>
   <si>
+    <t>1. Under "New User Signup!", enter the name and email. 2. Click Signup. 3. Click the Email field and try to type a different email (e.g., "changed@mailinator.com").</t>
+  </si>
+  <si>
     <t>Login with a valid email and password</t>
   </si>
   <si>
     <t>1. A registered account exists with name "Lara QA", email "lara.qa.tc01@mailinator.com", and password "Test1234". 2. The user is logged out. 3. The Home page is open in Chrome.</t>
   </si>
   <si>
+    <t>Mobile Number</t>
+  </si>
+  <si>
     <t>Email: lara.qa.tc01@mailinator.com / Password: Test1234</t>
   </si>
   <si>
+    <t>0812345678</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The Email field is grayed out, the mouse cursor shows a not-allowed symbol (🚫) over the field, and the email cannot be changed (it still shows </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>lara.qa.nocreate01@mailinator.com</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <t>Optional fields</t>
+  </si>
+  <si>
+    <t>Leave empty / unchecked</t>
+  </si>
+  <si>
+    <t>SECTION 2: Shared accounts and emails</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
     <t>1. Click Signup / Login in the header. 2. Enter the email in the Email Address field. 3. Enter the password in the Password field. 4. Click Login.</t>
   </si>
   <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
     <t>The Home page is displayed and the header shows "Logged in as Lara QA".</t>
   </si>
   <si>
-    <t>High</t>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>ACC-01</t>
+  </si>
+  <si>
+    <t>lara.qa.tc01@mailinator.com</t>
+  </si>
+  <si>
+    <t>Test1234</t>
   </si>
   <si>
     <t>TC-LOG-03</t>
   </si>
   <si>
+    <t>Registered account for Login tests and TC-REG-08, 16</t>
+  </si>
+  <si>
     <t>TS-LOG-03</t>
   </si>
   <si>
     <t>FR-LOG-08</t>
   </si>
   <si>
+    <t>NOCREATE-01</t>
+  </si>
+  <si>
+    <t>lara.qa.nocreate01@mailinator.com</t>
+  </si>
+  <si>
+    <t>nocreate001</t>
+  </si>
+  <si>
     <t>Logout button displayed after login</t>
+  </si>
+  <si>
+    <t>Signup tests that stop before Create Account. Never click Create Account with this email.</t>
+  </si>
+  <si>
+    <t>SECTION 3: Email naming rule for new accounts</t>
   </si>
   <si>
     <r>
@@ -134,22 +302,73 @@
     </r>
   </si>
   <si>
+    <t>lara.qa.[test case ID]@mailinator.com (e.g., lara.qa.reg05a@mailinator.com)</t>
+  </si>
+  <si>
+    <t>When re-running, add "-2", "-3" (e.g., lara.qa.reg05a-2@mailinator.com)</t>
+  </si>
+  <si>
+    <t>TC-REG-03</t>
+  </si>
+  <si>
+    <t>TS-REG-03</t>
+  </si>
+  <si>
+    <t>FR-REG-08</t>
+  </si>
+  <si>
+    <t>Name on the "Enter Account Information" page is editable</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.nocreate01@mailinator.com / New name: Lara Edited</t>
+  </si>
+  <si>
+    <t>1. Under "New User Signup!", enter the name and email. 2. Click Signup. 3. Click the Name field, delete "Lara QA" and type "Lara Edited".</t>
+  </si>
+  <si>
     <t>1. Look at the header.</t>
   </si>
   <si>
+    <t>The Name field accepts the change and shows the new name "Lara Edited".</t>
+  </si>
+  <si>
     <t>The header shows a Logout button.</t>
   </si>
   <si>
+    <t>TC-REG-04</t>
+  </si>
+  <si>
+    <t>TS-REG-04</t>
+  </si>
+  <si>
     <t>TC-LOG-04</t>
   </si>
   <si>
+    <t>FR-REG-11</t>
+  </si>
+  <si>
     <t>TS-LOG-04</t>
   </si>
   <si>
     <t>FR-LOG-09, FR-LOG-10</t>
   </si>
   <si>
+    <t>Account created with all required fields filled</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.reg04@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
     <t>Logout returns the user to the login form</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.reg04@mailinator.com / Password: register04 / Other fields: REG-VALID</t>
+  </si>
+  <si>
+    <t>1. Under "New User Signup!", enter the name and email. 2. Click Signup. 3. Enter the password in the Password field. 4. Fill in the other required fields using REG-VALID. 5. Click Create Account.</t>
+  </si>
+  <si>
+    <t>The system displays "Account Created!".</t>
   </si>
   <si>
     <r>
@@ -168,12 +387,33 @@
     </r>
   </si>
   <si>
+    <t>Creates an account. Use a new email (e.g., reg04-2) when re-running.</t>
+  </si>
+  <si>
     <t>1. Click Logout in the header.</t>
   </si>
   <si>
+    <t>TC-REG-05a</t>
+  </si>
+  <si>
+    <t>TS-REG-05</t>
+  </si>
+  <si>
     <t>1. The login form ("Login to your account") is displayed. 2. The header no longer shows "Logged in as Lara QA".</t>
   </si>
   <si>
+    <t>FR-REG-17</t>
+  </si>
+  <si>
+    <t>Password of 8 characters is accepted (BVA)</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.reg05a@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.reg05a@mailinator.com / Password: length08 / Other fields: REG-VALID</t>
+  </si>
+  <si>
     <t>TC-LOG-05</t>
   </si>
   <si>
@@ -186,6 +426,12 @@
     <t>Login fails with a wrong password</t>
   </si>
   <si>
+    <t>Creates an account. Use a new email (e.g., reg05a-2) when re-running.</t>
+  </si>
+  <si>
+    <t>TC-REG-05b</t>
+  </si>
+  <si>
     <t>Email: lara.qa.tc01@mailinator.com / Password: Wrong9999</t>
   </si>
   <si>
@@ -195,6 +441,15 @@
     <t>The message "Your email or password is incorrect!" is displayed, and the user is not logged in.</t>
   </si>
   <si>
+    <t>Password of 9 characters is accepted (BVA)</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.reg05b@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.reg05b@mailinator.com / Password: length009 / Other fields: REG-VALID</t>
+  </si>
+  <si>
     <t>TC-LOG-06</t>
   </si>
   <si>
@@ -205,6 +460,12 @@
   </si>
   <si>
     <t>Login fails with an unregistered email</t>
+  </si>
+  <si>
+    <t>Creates an account. Use a new email (e.g., reg05b-2) when re-running.</t>
+  </si>
+  <si>
+    <t>TC-REG-05c</t>
   </si>
   <si>
     <r>
@@ -224,81 +485,243 @@
     </r>
   </si>
   <si>
+    <t>Password of 10 characters is accepted (EP)</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.reg05c@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.reg05c@mailinator.com / Password: length0010 / Other fields: REG-VALID</t>
+  </si>
+  <si>
+    <t>Creates an account. Use a new email (e.g., reg05c-2) when re-running.</t>
+  </si>
+  <si>
+    <t>TC-REG-05d</t>
+  </si>
+  <si>
+    <t>Password of 19 characters is accepted (BVA)</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.reg05d@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.reg05d@mailinator.com / Password: lengthforpassword19 / Other fields: REG-VALID</t>
+  </si>
+  <si>
+    <t>Creates an account. Use a new email (e.g., reg05d-2) when re-running.</t>
+  </si>
+  <si>
+    <t>TC-REG-05e</t>
+  </si>
+  <si>
+    <t>Password of 20 characters is accepted (BVA)</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.reg05e@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.reg05e@mailinator.com / Password: lengthforpassword020 / Other fields: REG-VALID</t>
+  </si>
+  <si>
     <t>Email: lara.qa.notregistered01@mailinator.com / Password: Test1234</t>
   </si>
   <si>
+    <t>Creates an account. Use a new email (e.g., reg05e-2) when re-running.</t>
+  </si>
+  <si>
     <t>1. Click Signup / Login in the header. 2. Enter the unregistered email in the Email Address field. 3. Enter the password in the Password field. 4. Click Login.</t>
   </si>
   <si>
+    <t>TC-REG-05f</t>
+  </si>
+  <si>
+    <t>Password with letters, numbers, and symbols is accepted (EP)</t>
+  </si>
+  <si>
     <t>TC-LOG-07</t>
   </si>
   <si>
+    <t>1. No account exists with the email lara.qa.reg05f@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
     <t>TS-LOG-07</t>
   </si>
   <si>
+    <t>Name: Lara QA / Email: lara.qa.reg05f@mailinator.com / Password: p@ssword05 / Other fields: REG-VALID</t>
+  </si>
+  <si>
     <t>FR-LOG-02</t>
   </si>
   <si>
     <t>Login fails with empty Email Address</t>
   </si>
   <si>
+    <t>Creates an account. Use a new email (e.g., reg05f-2) when re-running. See RQ-11 (symbols allowed).</t>
+  </si>
+  <si>
     <t>Email: (empty) / Password: Test1234</t>
   </si>
   <si>
+    <t>TC-REG-06</t>
+  </si>
+  <si>
     <t>1. Click Signup / Login in the header. 2. Leave the Email Address field empty. 3. Enter the password in the Password field. 4. Click Login.</t>
   </si>
   <si>
+    <t>TS-REG-06</t>
+  </si>
+  <si>
+    <t>FR-REG-12</t>
+  </si>
+  <si>
     <t>The browser displays "Please fill out this field.", and the user is not logged in. (Chrome)</t>
   </si>
   <si>
+    <t>Home page with "Logged in as" after Continue</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.reg06@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.reg06@mailinator.com / Password: register06 / Other fields: REG-VALID</t>
+  </si>
+  <si>
     <t>TC-LOG-08</t>
   </si>
   <si>
+    <t>1. Under "New User Signup!", enter the name and email. 2. Click Signup. 3. Enter the password in the Password field. 4. Fill in the other required fields using REG-VALID. 5. Click Create Account. 6. Click Continue.</t>
+  </si>
+  <si>
     <t>TS-LOG-08</t>
   </si>
   <si>
+    <t>The Home page is displayed with "Logged in as Lara QA" in the header.</t>
+  </si>
+  <si>
     <t>FR-LOG-03</t>
   </si>
   <si>
     <t>Login fails with empty Password</t>
   </si>
   <si>
+    <t>Creates an account. Use a new email (e.g., reg06-2) when re-running.</t>
+  </si>
+  <si>
+    <t>TC-REG-07</t>
+  </si>
+  <si>
     <t>Email: lara.qa.tc01@mailinator.com / Password: (empty)</t>
   </si>
   <si>
+    <t>TS-REG-07</t>
+  </si>
+  <si>
+    <t>FR-REG-01</t>
+  </si>
+  <si>
     <t>1. Click Signup / Login in the header. 2. Enter the email in the Email Address field. 3. Leave the password field empty. 4. Click Login.</t>
   </si>
   <si>
+    <t>Email without a domain extension</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.reg07@mailinator. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.reg07@mailinator</t>
+  </si>
+  <si>
+    <t>1. Under "New User Signup!", enter the name and email without domain extension. 2. Click Signup.</t>
+  </si>
+  <si>
     <t>TC-LOG-09</t>
   </si>
   <si>
+    <t>"Please enter a valid email address." is displayed, and the "Enter Account Information" page does not appear.</t>
+  </si>
+  <si>
     <t>TS-LOG-09</t>
   </si>
   <si>
     <t>FR-LOG-12</t>
   </si>
   <si>
+    <t>Expected to fail, see OBS-01.</t>
+  </si>
+  <si>
     <t>Login with email in capital letters</t>
   </si>
   <si>
+    <t>TC-REG-08</t>
+  </si>
+  <si>
+    <t>TS-REG-08</t>
+  </si>
+  <si>
+    <t>FR-REG-02</t>
+  </si>
+  <si>
     <t>Email: LARA.QA.TC01@MAILINATOR.COM/ Password: Test1234</t>
   </si>
   <si>
+    <t>Registration fails with an already registered email</t>
+  </si>
+  <si>
+    <t>1. A registered account exists with email "lara.qa.tc01@mailinator.com". 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.tc01@mailinator.com</t>
+  </si>
+  <si>
+    <t>An error message saying the email already exists is displayed, and the "Enter Account Information" page does not appear.</t>
+  </si>
+  <si>
     <t>TC-LOG-10</t>
   </si>
   <si>
     <t>TS-LOG-10</t>
   </si>
   <si>
+    <t>The message currently has a grammar error, see OBS-02.</t>
+  </si>
+  <si>
     <t>FR-LOG-13</t>
   </si>
   <si>
+    <t>TC-REG-09</t>
+  </si>
+  <si>
     <t>Login with extra spaces around email</t>
   </si>
   <si>
+    <t>TS-REG-09</t>
+  </si>
+  <si>
+    <t>FR-REG-09</t>
+  </si>
+  <si>
     <t>Email: " lara.qa.tc01@mailinator.com " / Password: Test1234</t>
   </si>
   <si>
+    <t>Registration fails with empty name</t>
+  </si>
+  <si>
+    <t>Name: (empty) / Email: lara.qa.nocreate01@mailinator.com</t>
+  </si>
+  <si>
+    <t>1. Under "New User Signup!", leave the Name field empty and enter the email. 2. Click Signup.</t>
+  </si>
+  <si>
+    <t>The browser displays "Please fill out this field.", and the "Enter Account Information" page does not appear. (Chrome)</t>
+  </si>
+  <si>
+    <t>TC-REG-10</t>
+  </si>
+  <si>
+    <t>TS-REG-10</t>
+  </si>
+  <si>
     <t>TC-LOG-11</t>
   </si>
   <si>
@@ -308,43 +731,82 @@
     <t>None (new scenario)</t>
   </si>
   <si>
+    <t>Registration fails with Email Address empty</t>
+  </si>
+  <si>
+    <t>1. The user is logged out. 2. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
     <t>Log in after a failed login</t>
   </si>
   <si>
+    <t>Name: Lara QA / Email: (empty)</t>
+  </si>
+  <si>
+    <t>1. Under "New User Signup!", enter the name and leave the email empty. 2. Click Signup.</t>
+  </si>
+  <si>
     <t>Email: lara.qa.tc01@mailinator.com / Wrong Password: Wrong1234  / Correct Password: Test1234</t>
   </si>
   <si>
     <t>1. Click Signup / Login in the header. 2. Enter the email in the Email Address field. 3. Enter the wrong password in the Password field. 4. Click Login. 5. Check the login fails. 6. Enter the email and the right password again. 7. Click Login.</t>
   </si>
   <si>
+    <t>TC-REG-11a</t>
+  </si>
+  <si>
     <t>After step 4: "Your email or password is incorrect!" is displayed, and the user is not logged in. After step 7: The Home page is displayed and the header shows "Logged in as Lara QA".</t>
   </si>
   <si>
+    <t>TS-REG-11</t>
+  </si>
+  <si>
+    <t>FR-REG-10</t>
+  </si>
+  <si>
     <t>TC-LOG-12</t>
   </si>
   <si>
     <t>TS-LOG-12</t>
   </si>
   <si>
+    <t>Registration fails with Password field empty</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.reg11a@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
     <t>Password is masked</t>
   </si>
   <si>
     <t>Password: Test1234</t>
   </si>
   <si>
+    <t>Name: Lara QA / Email: lara.qa.reg11a@mailinator.com / Password: (empty) / Other fields: REG-VALID</t>
+  </si>
+  <si>
     <t>1. Click Signup / Login in the header. 2. Enter the password in the Password field. 3. Check the entered password is masked.</t>
   </si>
   <si>
     <t>The entered password is displayed as dots(.), not as readable text.</t>
   </si>
   <si>
+    <t>1. Under "New User Signup!", enter the name and email. 2. Click Signup. 3. Leave the Password field empty. 4. Fill in the other required fields using REG-VALID. 5. Click Create Account.</t>
+  </si>
+  <si>
     <t>TC-LOG-13</t>
   </si>
   <si>
+    <t>The browser displays "Please fill out this field." on the Password field, and the "Account Created!" page does not appear. (Chrome)</t>
+  </si>
+  <si>
     <t>TS-LOG-13</t>
   </si>
   <si>
     <t>Back button after logout</t>
+  </si>
+  <si>
+    <t>TC-REG-11b</t>
   </si>
   <si>
     <r>
@@ -363,25 +825,358 @@
     </r>
   </si>
   <si>
+    <t>Registration fails with First name field empty</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.reg11b@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
     <t>1. Click Logout in the header. 2. Click the browser's back button.</t>
   </si>
   <si>
+    <t>Name: Lara QA / Email: lara.qa.reg11b@mailinator.com / Password: register11 / Other fields: REG-VALID except First Name</t>
+  </si>
+  <si>
     <t>The header does not display "Logged in as Lara QA" and the Singup / Login link is displayed.</t>
   </si>
   <si>
+    <t>1. Under "New User Signup!", enter the name and email. 2. Click Signup. 3. Leave the First name field empty. 4. Fill in the other required fields using REG-VALID. 5. Click Create Account.</t>
+  </si>
+  <si>
+    <t>The browser displays "Please fill out this field." on the First name field, and the "Account Created!" page does not appear. (Chrome)</t>
+  </si>
+  <si>
     <t>TC-LOG-14</t>
   </si>
   <si>
     <t>TS-LOG-14</t>
   </si>
   <si>
+    <t>TC-REG-11c</t>
+  </si>
+  <si>
     <t>Login by pressing Enter</t>
   </si>
   <si>
+    <t>Registration fails with Last name field empty</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.reg11c@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.reg11c@mailinator.com / Password: register11 / Other fields: REG-VALID except Last Name</t>
+  </si>
+  <si>
     <t>1. Click Signup / Login in the header. 2. Enter the email in the Email Address field. 3. Enter the password in the Password field. 4. Press Enter on the keyboard.</t>
   </si>
   <si>
+    <t>1. Under "New User Signup!", enter the name and email. 2. Click Signup. 3. Leave the Last name field empty. 4. Fill in the other required fields using REG-VALID. 5. Click Create Account.</t>
+  </si>
+  <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>The browser displays "Please fill out this field." on the Last name field, and the "Account Created!" page does not appear. (Chrome)</t>
+  </si>
+  <si>
+    <t>TC-REG-11d</t>
+  </si>
+  <si>
+    <t>Registration fails with Address field empty</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.reg11d@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.reg11d@mailinator.com / Password: register11 / Other fields: REG-VALID except Address</t>
+  </si>
+  <si>
+    <t>1. Under "New User Signup!", enter the name and email. 2. Click Signup. 3. Leave the Address field empty. 4. Fill in the other required fields using REG-VALID. 5. Click Create Account.</t>
+  </si>
+  <si>
+    <t>The browser displays "Please fill out this field." on the Address field, and the "Account Created!" page does not appear. (Chrome)</t>
+  </si>
+  <si>
+    <t>TC-REG-11e</t>
+  </si>
+  <si>
+    <t>Registration fails with State field empty</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.reg11e@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.reg11e@mailinator.com / Password: register11 / Other fields: REG-VALID except State</t>
+  </si>
+  <si>
+    <t>1. Under "New User Signup!", enter the name and email. 2. Click Signup. 3. Leave the State field empty. 4. Fill in the other required fields using REG-VALID. 5. Click Create Account.</t>
+  </si>
+  <si>
+    <t>The browser displays "Please fill out this field." on the State field, and the "Account Created!" page does not appear. (Chrome)</t>
+  </si>
+  <si>
+    <t>TC-REG-11f</t>
+  </si>
+  <si>
+    <t>Registration fails with City field empty</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.reg11f@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.reg11f@mailinator.com / Password: register11 / Other fields: REG-VALID except City</t>
+  </si>
+  <si>
+    <t>1. Under "New User Signup!", enter the name and email. 2. Click Signup. 3. Leave the City field empty. 4. Fill in the other required fields using REG-VALID. 5. Click Create Account.</t>
+  </si>
+  <si>
+    <t>The browser displays "Please fill out this field." on the City field, and the "Account Created!" page does not appear. (Chrome)</t>
+  </si>
+  <si>
+    <t>TC-REG-11g</t>
+  </si>
+  <si>
+    <t>Registration fails with Zipcode field empty</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.reg11g@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.reg11g@mailinator.com / Password: register11 / Other fields: REG-VALID except Zipcode</t>
+  </si>
+  <si>
+    <t>1. Under "New User Signup!", enter the name and email. 2. Click Signup. 3. Leave the Zipcode field empty. 4. Fill in the other required fields using REG-VALID. 5. Click Create Account.</t>
+  </si>
+  <si>
+    <t>The browser displays "Please fill out this field." on the Zipcode field, and the "Account Created!" page does not appear. (Chrome)</t>
+  </si>
+  <si>
+    <t>TC-REG-11h</t>
+  </si>
+  <si>
+    <t>Registration fails with Mobile Number field empty</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.reg11h@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.reg11h@mailinator.com / Password: register11 / Other fields: REG-VALID except Mobile Number</t>
+  </si>
+  <si>
+    <t>1. Under "New User Signup!", enter the name and email. 2. Click Signup. 3. Leave the Mobile Number field empty. 4. Fill in the other required fields using REG-VALID. 5. Click Create Account.</t>
+  </si>
+  <si>
+    <t>The browser displays "Please fill out this field." on the Mobile Number field, and the "Account Created!" page does not appear. (Chrome)</t>
+  </si>
+  <si>
+    <t>TC-REG-12a</t>
+  </si>
+  <si>
+    <t>TS-REG-12</t>
+  </si>
+  <si>
+    <t>FR-REG-15</t>
+  </si>
+  <si>
+    <t>Password with letters only is rejected (EP)</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.reg12a@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.reg12a@mailinator.com / Password: registertwelve / Other fields: REG-VALID</t>
+  </si>
+  <si>
+    <t>"Password must be 8–20 characters and include at least one letter and one number." is displayed, and the "Account Created!" page does not appear.</t>
+  </si>
+  <si>
+    <t>Expected to fail, see OBS-05. The account may be created, so use a new email when re-running.</t>
+  </si>
+  <si>
+    <t>TC-REG-12b</t>
+  </si>
+  <si>
+    <t>Password with letters and symbols only is rejected (EP)</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.reg12b@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.reg12b@mailinator.com / Password: register@$ / Other fields: REG-VALID</t>
+  </si>
+  <si>
+    <t>TC-REG-13a</t>
+  </si>
+  <si>
+    <t>TS-REG-13</t>
+  </si>
+  <si>
+    <t>FR-REG-16</t>
+  </si>
+  <si>
+    <t>Password with numbers only is rejected (EP)</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.reg13a@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.reg13a@mailinator.com / Password: 00123456 / Other fields: REG-VALID</t>
+  </si>
+  <si>
+    <t>TC-REG-13b</t>
+  </si>
+  <si>
+    <t>Password with numbers and symbols only is rejected (EP)</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.reg13b@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.reg13b@mailinator.com / Password: @@123456 / Other fields: REG-VALID</t>
+  </si>
+  <si>
+    <t>TC-REG-14a</t>
+  </si>
+  <si>
+    <t>TS-REG-14</t>
+  </si>
+  <si>
+    <t>FR-REG-13</t>
+  </si>
+  <si>
+    <t>Password of 5 characters is rejected (EP)</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.reg14a@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.reg14a@mailinator.com / Password: len05 / Other fields: REG-VALID</t>
+  </si>
+  <si>
+    <t>TC-REG-14b</t>
+  </si>
+  <si>
+    <t>Password of 7 characters is rejected (BVA)</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.reg14b@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.reg14b@mailinator.com / Password: length7 / Other fields: REG-VALID</t>
+  </si>
+  <si>
+    <t>TC-REG-15a</t>
+  </si>
+  <si>
+    <t>TS-REG-15</t>
+  </si>
+  <si>
+    <t>FR-REG-14</t>
+  </si>
+  <si>
+    <t>Password of 21 characters is rejected (BVA)</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.reg15a@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.reg15a@mailinator.com / Password: lengthforpassword0021 / Other fields: REG-VALID</t>
+  </si>
+  <si>
+    <t>TC-REG-15b</t>
+  </si>
+  <si>
+    <t>Password of 23 characters is rejected (EP)</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.reg15b@mailinator.com. 2. The user is logged out. 3. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.reg15b@mailinator.com / Password: lengthforpassword000023 / Other fields: REG-VALID</t>
+  </si>
+  <si>
+    <t>TC-REG-16</t>
+  </si>
+  <si>
+    <t>TS-REG-16</t>
+  </si>
+  <si>
+    <t>Recover after a duplicate email</t>
+  </si>
+  <si>
+    <t>1. No account exists with the email lara.qa.nocreate01@mailinator.com. 2. An account exists with the email lara.qa.tc01@mailinator.com. 3. The user is logged out. 4. The Signup / Login page is open in Chrome.</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Registered Email: lara.qa.tc01@mailinator.com / Unregistered Email: lara.qa.nocreate01@mailinator.com</t>
+  </si>
+  <si>
+    <t>1. Under "New User Signup!", enter the name and registered email. 2. Click Signup. 3. Delete and enter unregistered email this time. 4. Click Signup again.</t>
+  </si>
+  <si>
+    <t>After step 2: An error message saying the email already exists is displayed. After step 4: The "Enter Account Information" page is displayed.</t>
+  </si>
+  <si>
+    <t>TC-REG-17</t>
+  </si>
+  <si>
+    <t>TS-REG-17</t>
+  </si>
+  <si>
+    <t>FR-REG-04</t>
+  </si>
+  <si>
+    <t>Name: Lara QA / Email: lara.qa.nocreate01@mailinator.com / Password: nocreate001</t>
+  </si>
+  <si>
+    <t>1. Under "New User Signup!", enter the name and email. 2. Click Signup. 3. Enter the password in the Password field.</t>
+  </si>
+  <si>
+    <t>The entered password is displayed as dots (•), not as readable text.</t>
+  </si>
+  <si>
+    <t>TC-REG-18</t>
+  </si>
+  <si>
+    <t>TS-REG-18</t>
+  </si>
+  <si>
+    <t>FR-REG-05</t>
+  </si>
+  <si>
+    <t>Email is pre-filled from the Signup form</t>
+  </si>
+  <si>
+    <t>The Email field shows "lara.qa.nocreate01@mailinator.com".</t>
+  </si>
+  <si>
+    <t>TC-REG-19</t>
+  </si>
+  <si>
+    <t>TS-REG-19</t>
+  </si>
+  <si>
+    <t>FR-REG-07</t>
+  </si>
+  <si>
+    <t>Name is pre-filled from the Signup form</t>
+  </si>
+  <si>
+    <t>The Name field shows "Lara QA".</t>
+  </si>
+  <si>
+    <t>TC-REG-20</t>
+  </si>
+  <si>
+    <t>TS-REG-20</t>
+  </si>
+  <si>
+    <t>Required fields are marked with *</t>
+  </si>
+  <si>
+    <t>1. Under "New User Signup!", enter the name and email. 2. Click Signup. 3. Look at the labels of the required fields.</t>
+  </si>
+  <si>
+    <t>Fields: Name, Email, Password, First name, Last name, Address, Country, State, City, Zipcode, Mobile Number are mark with *.</t>
   </si>
 </sst>
 </file>
@@ -423,7 +1218,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -431,9 +1226,15 @@
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -443,7 +1244,7 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -454,6 +1255,14 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -676,539 +1485,539 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>21</v>
+      <c r="A2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>21</v>
+      <c r="A3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="A4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>21</v>
+      <c r="E4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="G13" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="3" t="s">
+      <c r="H14" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
+      <c r="K14" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="G15" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="H9" s="3" t="s">
+      <c r="H15" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>21</v>
+      <c r="J15" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1220,4 +2029,1599 @@
   </hyperlinks>
   <drawing r:id="rId5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="11.25"/>
+    <col customWidth="1" min="3" max="3" width="16.38"/>
+    <col customWidth="1" min="4" max="4" width="13.88"/>
+    <col customWidth="1" min="5" max="5" width="56.25"/>
+    <col customWidth="1" min="6" max="6" width="112.5"/>
+    <col customWidth="1" min="7" max="7" width="95.88"/>
+    <col customWidth="1" min="8" max="8" width="160.5"/>
+    <col customWidth="1" min="9" max="9" width="138.38"/>
+    <col customWidth="1" min="12" max="12" width="74.5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="I3"/>
+  </hyperlinks>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="19.0"/>
+    <col customWidth="1" min="2" max="2" width="39.38"/>
+    <col customWidth="1" min="3" max="3" width="30.25"/>
+    <col customWidth="1" min="4" max="4" width="66.75"/>
+    <col customWidth="1" min="5" max="5" width="23.13"/>
+    <col customWidth="1" min="6" max="6" width="16.88"/>
+    <col customWidth="1" min="7" max="7" width="16.0"/>
+    <col customWidth="1" min="8" max="8" width="15.0"/>
+    <col customWidth="1" min="9" max="9" width="27.63"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="4">
+        <v>10110.0</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>